--- a/Bao-cao-KTPM/TestReport-GK.xlsx
+++ b/Bao-cao-KTPM/TestReport-GK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NguyenQuocKhanh\tester\QLDat_Ve\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NguyenQuocKhanh\tester\QLDat_Ve\Bao-cao-KTPM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6ED0A36-B5B6-44BD-85DA-1BE7A2252DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278A7358-2B4F-4577-9D9F-A7A987A2931F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D9C62906-688F-4723-BC95-DA80069B194D}"/>
   </bookViews>
@@ -168,9 +168,6 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -184,6 +181,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,220 +529,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>4</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7">
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>4</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7">
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>7</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>7</v>
       </c>
-      <c r="E9" s="7">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7">
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>15</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>12</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>3</v>
       </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7">
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
         <v>15</v>
       </c>
     </row>
